--- a/ec1a4c49009f919a31df9ea2526f0d30_38508e1bc518b6ba52f36d0e5cb6ee4e_8.xlsx
+++ b/ec1a4c49009f919a31df9ea2526f0d30_38508e1bc518b6ba52f36d0e5cb6ee4e_8.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26265" windowHeight="11625"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="26265" windowHeight="11625" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="基础" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,8 @@
     <sheet name="交付" sheetId="11" r:id="rId8"/>
     <sheet name="应急" sheetId="10" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -247,46 +248,58 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -294,6 +307,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -302,7 +316,8 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -310,6 +325,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -318,6 +334,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -326,6 +343,7 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -333,7 +351,8 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -341,7 +360,8 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -349,7 +369,8 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -357,14 +378,16 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -372,57 +395,49 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -474,19 +489,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -498,19 +513,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -522,19 +537,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -546,19 +561,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -570,19 +585,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -594,19 +609,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -617,118 +638,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -744,7 +653,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -753,16 +661,14 @@
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -777,7 +683,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -792,7 +697,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -807,7 +711,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -816,7 +719,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -827,309 +729,447 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="22">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="59">
+    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Percent" xfId="15"/>
+    <cellStyle name="Currency" xfId="16"/>
+    <cellStyle name="Currency [0]" xfId="17"/>
+    <cellStyle name="Comma" xfId="18"/>
+    <cellStyle name="Comma [0]" xfId="19"/>
+    <cellStyle name="Percent" xfId="20"/>
+    <cellStyle name="Currency" xfId="21"/>
+    <cellStyle name="Currency [0]" xfId="22"/>
+    <cellStyle name="Comma" xfId="23"/>
+    <cellStyle name="Comma [0]" xfId="24"/>
+    <cellStyle name="千位分隔" xfId="25"/>
+    <cellStyle name="货币" xfId="26"/>
+    <cellStyle name="百分比" xfId="27"/>
+    <cellStyle name="千位分隔[0]" xfId="28"/>
+    <cellStyle name="货币[0]" xfId="29"/>
+    <cellStyle name="超链接" xfId="30"/>
+    <cellStyle name="已访问的超链接" xfId="31"/>
+    <cellStyle name="注释" xfId="32"/>
+    <cellStyle name="警告文本" xfId="33"/>
+    <cellStyle name="标题" xfId="34"/>
+    <cellStyle name="解释性文本" xfId="35"/>
+    <cellStyle name="标题 1" xfId="36"/>
+    <cellStyle name="标题 2" xfId="37"/>
+    <cellStyle name="标题 3" xfId="38"/>
+    <cellStyle name="标题 4" xfId="39"/>
+    <cellStyle name="输入" xfId="40"/>
+    <cellStyle name="输出" xfId="41"/>
+    <cellStyle name="计算" xfId="42"/>
+    <cellStyle name="检查单元格" xfId="43"/>
+    <cellStyle name="链接单元格" xfId="44"/>
+    <cellStyle name="汇总" xfId="45"/>
+    <cellStyle name="好" xfId="46"/>
+    <cellStyle name="差" xfId="47"/>
+    <cellStyle name="适中" xfId="48"/>
+    <cellStyle name="强调文字颜色 1" xfId="49"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="50"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="51"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="52"/>
+    <cellStyle name="强调文字颜色 2" xfId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="54"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="55"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="56"/>
+    <cellStyle name="强调文字颜色 3" xfId="57"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="58"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="59"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="60"/>
+    <cellStyle name="强调文字颜色 4" xfId="61"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="62"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="63"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="64"/>
+    <cellStyle name="强调文字颜色 5" xfId="65"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="66"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="67"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="68"/>
+    <cellStyle name="强调文字颜色 6" xfId="69"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="70"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="71"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="72"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79998"/>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79998"/>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1140,7 +1180,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1168,36 +1208,36 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </horizontal>
       </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79998"/>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
       <border>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79998"/>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
       <border>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </bottom>
       </border>
     </dxf>
@@ -1212,19 +1252,19 @@
       </font>
       <border>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1239,59 +1279,59 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79998"/>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79998"/>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79998"/>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
       <border>
         <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </top>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79998"/>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
       <border>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1300,7 +1340,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1313,6 +1353,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1322,7 +1430,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1351,12 +1459,10 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="57785" y="1788795"/>
-          <a:ext cx="4188460" cy="1706880"/>
+          <a:off x="57150" y="1781175"/>
+          <a:ext cx="4181475" cy="1704975"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -1393,12 +1499,10 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5918200" y="1949450"/>
-          <a:ext cx="4629150" cy="2159000"/>
+          <a:off x="5905500" y="1943100"/>
+          <a:ext cx="4619625" cy="2162175"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -1411,7 +1515,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
@@ -1440,12 +1544,10 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7305675" y="407035"/>
-          <a:ext cx="3617595" cy="1587500"/>
+          <a:off x="7296150" y="409575"/>
+          <a:ext cx="3609975" cy="1590675"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -1482,12 +1584,10 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="203835" y="2689860"/>
-          <a:ext cx="4817110" cy="1330960"/>
+          <a:off x="200025" y="2686050"/>
+          <a:ext cx="4810125" cy="1333500"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -1524,12 +1624,10 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5791835" y="2807970"/>
-          <a:ext cx="4265295" cy="1397635"/>
+          <a:off x="5781675" y="2809875"/>
+          <a:ext cx="4267200" cy="1400175"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -1542,7 +1640,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1571,12 +1669,10 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5080" y="2305050"/>
-          <a:ext cx="3688715" cy="952500"/>
+          <a:off x="9525" y="2305050"/>
+          <a:ext cx="3686175" cy="952500"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -1613,12 +1709,10 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4109720" y="2439670"/>
-          <a:ext cx="4099560" cy="884555"/>
+          <a:off x="4105275" y="2438400"/>
+          <a:ext cx="4086225" cy="885825"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -1631,7 +1725,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1660,12 +1754,10 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1929130"/>
-          <a:ext cx="2931795" cy="971550"/>
+          <a:off x="0" y="1933575"/>
+          <a:ext cx="2933700" cy="971550"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -1678,7 +1770,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -1701,19 +1793,17 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId1"/>
-        <a:srcRect l="7626"/>
+        <a:srcRect l="7623"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="771525" y="2151380"/>
-          <a:ext cx="1998980" cy="848995"/>
+          <a:off x="771525" y="2152650"/>
+          <a:ext cx="1990725" cy="847725"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -1744,19 +1834,17 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId2"/>
-        <a:srcRect r="23400"/>
+        <a:srcRect r="23397"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3129915" y="2279015"/>
-          <a:ext cx="2208530" cy="753745"/>
+          <a:off x="3124200" y="2276475"/>
+          <a:ext cx="2200275" cy="752475"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -1787,19 +1875,17 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId3"/>
-        <a:srcRect l="4881" t="5356"/>
+        <a:srcRect l="4878" t="5354"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5562600" y="2318385"/>
-          <a:ext cx="2513965" cy="706755"/>
+          <a:off x="5543550" y="2314575"/>
+          <a:ext cx="2505075" cy="704850"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -1812,7 +1898,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1841,12 +1927,10 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="205740" y="1242695"/>
-          <a:ext cx="3797935" cy="2134235"/>
+          <a:off x="209550" y="1238250"/>
+          <a:ext cx="3790950" cy="2133600"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -1877,19 +1961,17 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId2"/>
-        <a:srcRect r="20364"/>
+        <a:srcRect r="20361"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4339590" y="1340485"/>
-          <a:ext cx="2914015" cy="2450465"/>
+          <a:off x="4324350" y="1343025"/>
+          <a:ext cx="2905125" cy="2447925"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -1926,12 +2008,10 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7651115" y="1426210"/>
-          <a:ext cx="4789805" cy="2289175"/>
+          <a:off x="7629525" y="1428750"/>
+          <a:ext cx="4772025" cy="2286000"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -1944,7 +2024,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1973,12 +2053,10 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="109855" y="1313815"/>
-          <a:ext cx="3268980" cy="1914525"/>
+          <a:off x="114300" y="1314450"/>
+          <a:ext cx="3257550" cy="1914525"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -2015,12 +2093,10 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3785870" y="1247775"/>
-          <a:ext cx="3726180" cy="2114550"/>
+          <a:off x="3771900" y="1247775"/>
+          <a:ext cx="3714750" cy="2114550"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -2057,12 +2133,10 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7964170" y="1139190"/>
-          <a:ext cx="3671570" cy="2146300"/>
+          <a:off x="7943850" y="1143000"/>
+          <a:ext cx="3657600" cy="2143125"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
@@ -2323,31 +2397,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A2:I41"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9.26666666666667" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.26666666666667" style="2"/>
-    <col min="2" max="2" width="23.5666666666667" style="3" customWidth="1"/>
-    <col min="3" max="3" width="21.7833333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.1083333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1083333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.425" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.26666666666667" style="1"/>
+    <col min="1" max="1" width="9.25" style="2"/>
+    <col min="2" max="2" width="23.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.375" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.25" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" s="1" customFormat="1" spans="1:9">
+    <row r="1" spans="1:9" ht="14.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="14.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:9">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="14.25">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
+      <c r="C3" s="1"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7" t="s">
         <v>1</v>
@@ -2356,8 +2448,13 @@
       <c r="G3" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:9">
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="14.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
       <c r="D4" s="8" t="s">
         <v>3</v>
       </c>
@@ -2373,13 +2470,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:9">
+    <row r="5" spans="1:9" s="1" customFormat="1" ht="14.25">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="C5" s="1"/>
       <c r="D5" s="13" t="s">
         <v>8</v>
       </c>
@@ -2391,9 +2489,10 @@
       <c r="H5" s="16"/>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:9">
+    <row r="6" spans="1:9" s="1" customFormat="1" ht="14.25">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
+      <c r="C6" s="1"/>
       <c r="D6" s="13" t="s">
         <v>10</v>
       </c>
@@ -2407,9 +2506,10 @@
       <c r="H6" s="16"/>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:9">
+    <row r="7" spans="1:9" s="1" customFormat="1" ht="14.25">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
+      <c r="C7" s="1"/>
       <c r="D7" s="13"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18" t="s">
@@ -2421,7 +2521,7 @@
       <c r="H7" s="16"/>
       <c r="I7" s="12"/>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:9">
+    <row r="8" spans="1:9" s="1" customFormat="1" ht="14.25">
       <c r="A8" s="2">
         <v>3</v>
       </c>
@@ -2444,11 +2544,12 @@
       <c r="H8" s="16"/>
       <c r="I8" s="12"/>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:9">
+    <row r="9" spans="1:9" s="1" customFormat="1" ht="14.25">
       <c r="A9" s="2"/>
       <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="C9" s="1"/>
       <c r="D9" s="13"/>
       <c r="E9" s="17"/>
       <c r="F9" s="18" t="s">
@@ -2458,9 +2559,10 @@
       <c r="H9" s="16"/>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:9">
+    <row r="10" spans="1:9" s="1" customFormat="1" ht="14.25">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
+      <c r="C10" s="1"/>
       <c r="D10" s="13" t="s">
         <v>21</v>
       </c>
@@ -2474,9 +2576,10 @@
       <c r="H10" s="16"/>
       <c r="I10" s="12"/>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:9">
+    <row r="11" spans="1:9" s="1" customFormat="1" ht="14.25">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
+      <c r="C11" s="1"/>
       <c r="D11" s="13" t="s">
         <v>23</v>
       </c>
@@ -2488,9 +2591,10 @@
       <c r="H11" s="16"/>
       <c r="I11" s="12"/>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:9">
+    <row r="12" spans="1:9" s="1" customFormat="1" ht="14.25">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
+      <c r="C12" s="1"/>
       <c r="D12" s="19" t="s">
         <v>24</v>
       </c>
@@ -2504,68 +2608,111 @@
       <c r="H12" s="21"/>
       <c r="I12" s="12"/>
     </row>
-    <row r="14" s="1" customFormat="1"/>
-    <row r="15" spans="1:9">
+    <row r="13" spans="1:9" ht="14.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" s="1" customFormat="1" ht="14.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" ht="14.25">
       <c r="A15" s="2">
         <v>4</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:9">
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" s="1" customFormat="1" ht="14.25">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" ht="14.25">
       <c r="A17" s="2">
         <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="19" customFormat="1" ht="13.5"/>
-    <row r="20" customFormat="1" ht="13.5"/>
-    <row r="21" customFormat="1" ht="13.5"/>
-    <row r="22" s="1" customFormat="1" spans="1:2">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="19" ht="13.5"/>
+    <row r="20" ht="13.5"/>
+    <row r="21" ht="13.5"/>
+    <row r="22" spans="1:2" s="1" customFormat="1" ht="14.25">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
     </row>
-    <row r="23" customFormat="1" ht="13.5"/>
-    <row r="25" customFormat="1" ht="13.5"/>
-    <row r="27" customFormat="1" ht="13.5"/>
-    <row r="29" customFormat="1" ht="13.5"/>
-    <row r="31" customFormat="1" ht="13.5"/>
-    <row r="33" customFormat="1" ht="13.5"/>
-    <row r="34" customFormat="1" ht="13.5"/>
-    <row r="35" customFormat="1" ht="13.5"/>
-    <row r="37" customFormat="1" ht="13.5"/>
-    <row r="39" customFormat="1" ht="13.5"/>
-    <row r="41" customFormat="1" ht="13.5"/>
+    <row r="23" ht="13.5"/>
+    <row r="25" ht="13.5"/>
+    <row r="27" ht="13.5"/>
+    <row r="29" ht="13.5"/>
+    <row r="31" ht="13.5"/>
+    <row r="33" ht="13.5"/>
+    <row r="34" ht="13.5"/>
+    <row r="35" ht="13.5"/>
+    <row r="37" ht="13.5"/>
+    <row r="39" ht="13.5"/>
+    <row r="41" ht="13.5"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="H4:H12"/>
     <mergeCell ref="I4:I12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:O8"/>
   <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
-    <col min="2" max="2" width="11.3166666666667" customWidth="1"/>
+    <col min="2" max="2" width="11.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="24" spans="1:15">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="24">
       <c r="A1" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="B1" s="1"/>
       <c r="C1" s="4" t="s">
         <v>28</v>
       </c>
@@ -2580,15 +2727,19 @@
       <c r="J1" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
       <c r="N1" s="6" t="s">
         <v>31</v>
       </c>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="32" customHeight="1" spans="1:15">
+    <row r="2" spans="1:15" s="1" customFormat="1" ht="32" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="B2" s="1"/>
       <c r="C2" s="4" t="s">
         <v>33</v>
       </c>
@@ -2603,23 +2754,38 @@
       <c r="J2" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="14.25" spans="1:15">
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="14.25">
       <c r="A3" s="3"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" ht="13.5">
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" ht="13.5">
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
     </row>
-    <row r="6" ht="14.25" spans="1:15">
+    <row r="6" spans="1:14" ht="14.25">
       <c r="A6" s="1" t="s">
         <v>36</v>
       </c>
@@ -2630,7 +2796,8 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="7" spans="1:14" ht="13.5"/>
+    <row r="8" spans="1:14" ht="13.5">
       <c r="B8" t="s">
         <v>37</v>
       </c>
@@ -2645,50 +2812,74 @@
     <mergeCell ref="N1:O5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
+  <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="13.8416666666667" customWidth="1"/>
-    <col min="8" max="8" width="42.2166666666667" customWidth="1"/>
+    <col min="2" max="2" width="13.875" customWidth="1"/>
+    <col min="8" max="8" width="42.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:9">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="14.25">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>39</v>
       </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
       <c r="I1" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" ht="13.5">
       <c r="C2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="14.25" spans="1:9">
+    <row r="3" spans="1:9" ht="13.5"/>
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="14.25">
       <c r="A4" s="2"/>
       <c r="B4" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" ht="13.5">
       <c r="C5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="14.25" spans="1:9">
+    <row r="6" spans="1:9" s="1" customFormat="1" ht="14.25">
       <c r="A6" s="2"/>
-    </row>
-    <row r="9" ht="14.25" spans="1:9">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" ht="13.5"/>
+    <row r="8" spans="1:9" ht="13.5"/>
+    <row r="9" spans="1:9" ht="14.25">
       <c r="B9" s="3" t="s">
         <v>44</v>
       </c>
@@ -2696,7 +2887,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="10" spans="1:9" ht="13.5"/>
+    <row r="11" spans="1:9" ht="13.5"/>
+    <row r="12" spans="1:9" ht="13.5"/>
+    <row r="13" spans="1:9" ht="13.5"/>
+    <row r="14" spans="1:9" ht="13.5"/>
+    <row r="15" spans="1:9" ht="13.5">
       <c r="B15" t="s">
         <v>46</v>
       </c>
@@ -2706,22 +2902,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
+  <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="20.6833333333333" customWidth="1"/>
-    <col min="4" max="4" width="25.1583333333333" customWidth="1"/>
+    <col min="2" max="2" width="20.625" customWidth="1"/>
+    <col min="4" max="4" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:5">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="14.25">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>48</v>
@@ -2729,26 +2925,27 @@
       <c r="C1" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="D1" s="1"/>
       <c r="E1" s="1" t="s">
         <v>50</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="23.9" customWidth="1"/>
+    <col min="2" max="2" width="23.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:3">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="14.25">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>51</v>
@@ -2757,33 +2954,34 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" ht="14.25" spans="1:3">
+    <row r="2" spans="1:3" ht="14.25">
       <c r="C2" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="3" spans="1:3" ht="13.5"/>
+    <row r="4" spans="1:3" ht="13.5">
       <c r="C4" t="s">
         <v>54</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
+  <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="23.575" customWidth="1"/>
+    <col min="1" max="1" width="23.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:2">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="14.25">
       <c r="A1" s="3" t="s">
         <v>55</v>
       </c>
@@ -2791,13 +2989,13 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="24" customHeight="1" spans="1:2">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="24" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="14.25" spans="1:2">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="14.25">
       <c r="A3" s="3"/>
       <c r="B3" s="1" t="s">
         <v>58</v>
@@ -2805,47 +3003,57 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
+  <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:2">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="14.25">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="2" spans="1:2" ht="13.5"/>
+    <row r="3" spans="1:2" ht="13.5"/>
+    <row r="4" spans="1:2" ht="13.5"/>
+    <row r="5" spans="1:2" ht="13.5">
       <c r="B5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="6" spans="1:2" ht="13.5"/>
+    <row r="7" spans="1:2" ht="13.5"/>
+    <row r="8" spans="1:2" ht="13.5"/>
+    <row r="9" spans="1:2" ht="13.5"/>
+    <row r="10" spans="1:2" ht="13.5"/>
+    <row r="11" spans="1:2" ht="13.5">
       <c r="B11" t="s">
         <v>61</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
+  <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A3:I5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <sheetData>
-    <row r="3" s="1" customFormat="1" ht="14.25" spans="1:9">
+    <row r="1" spans="1:3" ht="13.5"/>
+    <row r="2" spans="1:3" ht="13.5"/>
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="14.25">
       <c r="A3" s="2"/>
       <c r="B3" s="3" t="s">
         <v>62</v>
@@ -2858,25 +3066,26 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="4" spans="1:3" ht="13.5"/>
+    <row r="5" spans="1:3" ht="13.5">
       <c r="C5" t="s">
         <v>63</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
+  <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="9.025" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:9">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="14.25">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>64</v>
@@ -2889,14 +3098,16 @@
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="2" spans="1:3" ht="13.5"/>
+    <row r="3" spans="1:3" ht="13.5">
       <c r="C3" t="s">
         <v>63</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
+  <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>